--- a/data/2026-05-04/BallparkPal_Games.xlsx
+++ b/data/2026-05-04/BallparkPal_Games.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="65">
   <si>
     <t>GamePk</t>
   </si>
@@ -135,6 +135,81 @@
   </si>
   <si>
     <t>Runs20</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>HOU</t>
+  </si>
+  <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
+    <t>CHC</t>
   </si>
 </sst>
 </file>
@@ -474,7 +549,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -597,6 +672,1470 @@
       </c>
       <c r="AN1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="A2">
+        <v>822984</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2">
+        <v>4.169</v>
+      </c>
+      <c r="F2">
+        <v>4.161</v>
+      </c>
+      <c r="G2">
+        <v>0.481</v>
+      </c>
+      <c r="H2">
+        <v>0.519</v>
+      </c>
+      <c r="I2">
+        <v>0.246</v>
+      </c>
+      <c r="J2">
+        <v>0.105</v>
+      </c>
+      <c r="K2">
+        <v>0.13</v>
+      </c>
+      <c r="L2">
+        <v>0.236</v>
+      </c>
+      <c r="M2">
+        <v>0.1</v>
+      </c>
+      <c r="N2">
+        <v>0.183</v>
+      </c>
+      <c r="O2">
+        <v>0.536</v>
+      </c>
+      <c r="P2">
+        <v>2.277</v>
+      </c>
+      <c r="Q2">
+        <v>2.57</v>
+      </c>
+      <c r="R2">
+        <v>0.39</v>
+      </c>
+      <c r="S2">
+        <v>0.456</v>
+      </c>
+      <c r="T2">
+        <v>0.0</v>
+      </c>
+      <c r="U2">
+        <v>0.019</v>
+      </c>
+      <c r="V2">
+        <v>0.022</v>
+      </c>
+      <c r="W2">
+        <v>0.061</v>
+      </c>
+      <c r="X2">
+        <v>0.049</v>
+      </c>
+      <c r="Y2">
+        <v>0.11</v>
+      </c>
+      <c r="Z2">
+        <v>0.084</v>
+      </c>
+      <c r="AA2">
+        <v>0.12</v>
+      </c>
+      <c r="AB2">
+        <v>0.084</v>
+      </c>
+      <c r="AC2">
+        <v>0.107</v>
+      </c>
+      <c r="AD2">
+        <v>0.079</v>
+      </c>
+      <c r="AE2">
+        <v>0.07</v>
+      </c>
+      <c r="AF2">
+        <v>0.045</v>
+      </c>
+      <c r="AG2">
+        <v>0.051</v>
+      </c>
+      <c r="AH2">
+        <v>0.029</v>
+      </c>
+      <c r="AI2">
+        <v>0.021</v>
+      </c>
+      <c r="AJ2">
+        <v>0.012</v>
+      </c>
+      <c r="AK2">
+        <v>0.011</v>
+      </c>
+      <c r="AL2">
+        <v>0.008</v>
+      </c>
+      <c r="AM2">
+        <v>0.006</v>
+      </c>
+      <c r="AN2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3">
+        <v>823064</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>5.345</v>
+      </c>
+      <c r="F3">
+        <v>4.664</v>
+      </c>
+      <c r="G3">
+        <v>0.533</v>
+      </c>
+      <c r="H3">
+        <v>0.467</v>
+      </c>
+      <c r="I3">
+        <v>0.318</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>0.115</v>
+      </c>
+      <c r="L3">
+        <v>0.21</v>
+      </c>
+      <c r="M3">
+        <v>0.097</v>
+      </c>
+      <c r="N3">
+        <v>0.161</v>
+      </c>
+      <c r="O3">
+        <v>0.56</v>
+      </c>
+      <c r="P3">
+        <v>3.025</v>
+      </c>
+      <c r="Q3">
+        <v>2.769</v>
+      </c>
+      <c r="R3">
+        <v>0.463</v>
+      </c>
+      <c r="S3">
+        <v>0.409</v>
+      </c>
+      <c r="T3">
+        <v>0.0</v>
+      </c>
+      <c r="U3">
+        <v>0.006</v>
+      </c>
+      <c r="V3">
+        <v>0.01</v>
+      </c>
+      <c r="W3">
+        <v>0.032</v>
+      </c>
+      <c r="X3">
+        <v>0.039</v>
+      </c>
+      <c r="Y3">
+        <v>0.077</v>
+      </c>
+      <c r="Z3">
+        <v>0.063</v>
+      </c>
+      <c r="AA3">
+        <v>0.105</v>
+      </c>
+      <c r="AB3">
+        <v>0.077</v>
+      </c>
+      <c r="AC3">
+        <v>0.103</v>
+      </c>
+      <c r="AD3">
+        <v>0.072</v>
+      </c>
+      <c r="AE3">
+        <v>0.086</v>
+      </c>
+      <c r="AF3">
+        <v>0.051</v>
+      </c>
+      <c r="AG3">
+        <v>0.072</v>
+      </c>
+      <c r="AH3">
+        <v>0.049</v>
+      </c>
+      <c r="AI3">
+        <v>0.044</v>
+      </c>
+      <c r="AJ3">
+        <v>0.027</v>
+      </c>
+      <c r="AK3">
+        <v>0.026</v>
+      </c>
+      <c r="AL3">
+        <v>0.014</v>
+      </c>
+      <c r="AM3">
+        <v>0.016</v>
+      </c>
+      <c r="AN3">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4">
+        <v>823143</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4">
+        <v>4.163</v>
+      </c>
+      <c r="F4">
+        <v>4.721</v>
+      </c>
+      <c r="G4">
+        <v>0.419</v>
+      </c>
+      <c r="H4">
+        <v>0.581</v>
+      </c>
+      <c r="I4">
+        <v>0.214</v>
+      </c>
+      <c r="J4">
+        <v>0.087</v>
+      </c>
+      <c r="K4">
+        <v>0.118</v>
+      </c>
+      <c r="L4">
+        <v>0.301</v>
+      </c>
+      <c r="M4">
+        <v>0.108</v>
+      </c>
+      <c r="N4">
+        <v>0.172</v>
+      </c>
+      <c r="O4">
+        <v>0.523</v>
+      </c>
+      <c r="P4">
+        <v>2.33</v>
+      </c>
+      <c r="Q4">
+        <v>2.829</v>
+      </c>
+      <c r="R4">
+        <v>0.369</v>
+      </c>
+      <c r="S4">
+        <v>0.49</v>
+      </c>
+      <c r="T4">
+        <v>0.0</v>
+      </c>
+      <c r="U4">
+        <v>0.012</v>
+      </c>
+      <c r="V4">
+        <v>0.013</v>
+      </c>
+      <c r="W4">
+        <v>0.059</v>
+      </c>
+      <c r="X4">
+        <v>0.051</v>
+      </c>
+      <c r="Y4">
+        <v>0.092</v>
+      </c>
+      <c r="Z4">
+        <v>0.078</v>
+      </c>
+      <c r="AA4">
+        <v>0.113</v>
+      </c>
+      <c r="AB4">
+        <v>0.078</v>
+      </c>
+      <c r="AC4">
+        <v>0.11</v>
+      </c>
+      <c r="AD4">
+        <v>0.067</v>
+      </c>
+      <c r="AE4">
+        <v>0.089</v>
+      </c>
+      <c r="AF4">
+        <v>0.051</v>
+      </c>
+      <c r="AG4">
+        <v>0.051</v>
+      </c>
+      <c r="AH4">
+        <v>0.041</v>
+      </c>
+      <c r="AI4">
+        <v>0.032</v>
+      </c>
+      <c r="AJ4">
+        <v>0.018</v>
+      </c>
+      <c r="AK4">
+        <v>0.015</v>
+      </c>
+      <c r="AL4">
+        <v>0.011</v>
+      </c>
+      <c r="AM4">
+        <v>0.009</v>
+      </c>
+      <c r="AN4">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40">
+      <c r="A5">
+        <v>823228</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>4.419</v>
+      </c>
+      <c r="F5">
+        <v>3.874</v>
+      </c>
+      <c r="G5">
+        <v>0.531</v>
+      </c>
+      <c r="H5">
+        <v>0.469</v>
+      </c>
+      <c r="I5">
+        <v>0.301</v>
+      </c>
+      <c r="J5">
+        <v>0.095</v>
+      </c>
+      <c r="K5">
+        <v>0.135</v>
+      </c>
+      <c r="L5">
+        <v>0.2</v>
+      </c>
+      <c r="M5">
+        <v>0.094</v>
+      </c>
+      <c r="N5">
+        <v>0.175</v>
+      </c>
+      <c r="O5">
+        <v>0.425</v>
+      </c>
+      <c r="P5">
+        <v>2.211</v>
+      </c>
+      <c r="Q5">
+        <v>2.143</v>
+      </c>
+      <c r="R5">
+        <v>0.426</v>
+      </c>
+      <c r="S5">
+        <v>0.404</v>
+      </c>
+      <c r="T5">
+        <v>0.0</v>
+      </c>
+      <c r="U5">
+        <v>0.023</v>
+      </c>
+      <c r="V5">
+        <v>0.022</v>
+      </c>
+      <c r="W5">
+        <v>0.076</v>
+      </c>
+      <c r="X5">
+        <v>0.063</v>
+      </c>
+      <c r="Y5">
+        <v>0.106</v>
+      </c>
+      <c r="Z5">
+        <v>0.079</v>
+      </c>
+      <c r="AA5">
+        <v>0.115</v>
+      </c>
+      <c r="AB5">
+        <v>0.089</v>
+      </c>
+      <c r="AC5">
+        <v>0.09</v>
+      </c>
+      <c r="AD5">
+        <v>0.06</v>
+      </c>
+      <c r="AE5">
+        <v>0.071</v>
+      </c>
+      <c r="AF5">
+        <v>0.043</v>
+      </c>
+      <c r="AG5">
+        <v>0.041</v>
+      </c>
+      <c r="AH5">
+        <v>0.03</v>
+      </c>
+      <c r="AI5">
+        <v>0.029</v>
+      </c>
+      <c r="AJ5">
+        <v>0.019</v>
+      </c>
+      <c r="AK5">
+        <v>0.018</v>
+      </c>
+      <c r="AL5">
+        <v>0.007</v>
+      </c>
+      <c r="AM5">
+        <v>0.006</v>
+      </c>
+      <c r="AN5">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
+      <c r="A6">
+        <v>823552</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>3.535</v>
+      </c>
+      <c r="F6">
+        <v>5.562</v>
+      </c>
+      <c r="G6">
+        <v>0.285</v>
+      </c>
+      <c r="H6">
+        <v>0.715</v>
+      </c>
+      <c r="I6">
+        <v>0.137</v>
+      </c>
+      <c r="J6">
+        <v>0.061</v>
+      </c>
+      <c r="K6">
+        <v>0.087</v>
+      </c>
+      <c r="L6">
+        <v>0.433</v>
+      </c>
+      <c r="M6">
+        <v>0.121</v>
+      </c>
+      <c r="N6">
+        <v>0.161</v>
+      </c>
+      <c r="O6">
+        <v>0.506</v>
+      </c>
+      <c r="P6">
+        <v>1.612</v>
+      </c>
+      <c r="Q6">
+        <v>3.361</v>
+      </c>
+      <c r="R6">
+        <v>0.225</v>
+      </c>
+      <c r="S6">
+        <v>0.631</v>
+      </c>
+      <c r="T6">
+        <v>0.0</v>
+      </c>
+      <c r="U6">
+        <v>0.014</v>
+      </c>
+      <c r="V6">
+        <v>0.016</v>
+      </c>
+      <c r="W6">
+        <v>0.051</v>
+      </c>
+      <c r="X6">
+        <v>0.049</v>
+      </c>
+      <c r="Y6">
+        <v>0.09</v>
+      </c>
+      <c r="Z6">
+        <v>0.079</v>
+      </c>
+      <c r="AA6">
+        <v>0.109</v>
+      </c>
+      <c r="AB6">
+        <v>0.089</v>
+      </c>
+      <c r="AC6">
+        <v>0.097</v>
+      </c>
+      <c r="AD6">
+        <v>0.068</v>
+      </c>
+      <c r="AE6">
+        <v>0.078</v>
+      </c>
+      <c r="AF6">
+        <v>0.054</v>
+      </c>
+      <c r="AG6">
+        <v>0.052</v>
+      </c>
+      <c r="AH6">
+        <v>0.036</v>
+      </c>
+      <c r="AI6">
+        <v>0.033</v>
+      </c>
+      <c r="AJ6">
+        <v>0.02</v>
+      </c>
+      <c r="AK6">
+        <v>0.017</v>
+      </c>
+      <c r="AL6">
+        <v>0.014</v>
+      </c>
+      <c r="AM6">
+        <v>0.011</v>
+      </c>
+      <c r="AN6">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40">
+      <c r="A7">
+        <v>823874</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7">
+        <v>4.453</v>
+      </c>
+      <c r="F7">
+        <v>3.658</v>
+      </c>
+      <c r="G7">
+        <v>0.569</v>
+      </c>
+      <c r="H7">
+        <v>0.431</v>
+      </c>
+      <c r="I7">
+        <v>0.322</v>
+      </c>
+      <c r="J7">
+        <v>0.102</v>
+      </c>
+      <c r="K7">
+        <v>0.145</v>
+      </c>
+      <c r="L7">
+        <v>0.178</v>
+      </c>
+      <c r="M7">
+        <v>0.088</v>
+      </c>
+      <c r="N7">
+        <v>0.165</v>
+      </c>
+      <c r="O7">
+        <v>0.484</v>
+      </c>
+      <c r="P7">
+        <v>2.43</v>
+      </c>
+      <c r="Q7">
+        <v>2.04</v>
+      </c>
+      <c r="R7">
+        <v>0.469</v>
+      </c>
+      <c r="S7">
+        <v>0.367</v>
+      </c>
+      <c r="T7">
+        <v>0.0</v>
+      </c>
+      <c r="U7">
+        <v>0.021</v>
+      </c>
+      <c r="V7">
+        <v>0.02</v>
+      </c>
+      <c r="W7">
+        <v>0.073</v>
+      </c>
+      <c r="X7">
+        <v>0.061</v>
+      </c>
+      <c r="Y7">
+        <v>0.116</v>
+      </c>
+      <c r="Z7">
+        <v>0.082</v>
+      </c>
+      <c r="AA7">
+        <v>0.12</v>
+      </c>
+      <c r="AB7">
+        <v>0.083</v>
+      </c>
+      <c r="AC7">
+        <v>0.103</v>
+      </c>
+      <c r="AD7">
+        <v>0.063</v>
+      </c>
+      <c r="AE7">
+        <v>0.07</v>
+      </c>
+      <c r="AF7">
+        <v>0.053</v>
+      </c>
+      <c r="AG7">
+        <v>0.042</v>
+      </c>
+      <c r="AH7">
+        <v>0.023</v>
+      </c>
+      <c r="AI7">
+        <v>0.025</v>
+      </c>
+      <c r="AJ7">
+        <v>0.013</v>
+      </c>
+      <c r="AK7">
+        <v>0.016</v>
+      </c>
+      <c r="AL7">
+        <v>0.007</v>
+      </c>
+      <c r="AM7">
+        <v>0.004</v>
+      </c>
+      <c r="AN7">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40">
+      <c r="A8">
+        <v>824039</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <v>4.166</v>
+      </c>
+      <c r="F8">
+        <v>5.069</v>
+      </c>
+      <c r="G8">
+        <v>0.39</v>
+      </c>
+      <c r="H8">
+        <v>0.61</v>
+      </c>
+      <c r="I8">
+        <v>0.203</v>
+      </c>
+      <c r="J8">
+        <v>0.081</v>
+      </c>
+      <c r="K8">
+        <v>0.106</v>
+      </c>
+      <c r="L8">
+        <v>0.331</v>
+      </c>
+      <c r="M8">
+        <v>0.105</v>
+      </c>
+      <c r="N8">
+        <v>0.173</v>
+      </c>
+      <c r="O8">
+        <v>0.506</v>
+      </c>
+      <c r="P8">
+        <v>2.032</v>
+      </c>
+      <c r="Q8">
+        <v>2.911</v>
+      </c>
+      <c r="R8">
+        <v>0.309</v>
+      </c>
+      <c r="S8">
+        <v>0.536</v>
+      </c>
+      <c r="T8">
+        <v>0.0</v>
+      </c>
+      <c r="U8">
+        <v>0.018</v>
+      </c>
+      <c r="V8">
+        <v>0.012</v>
+      </c>
+      <c r="W8">
+        <v>0.055</v>
+      </c>
+      <c r="X8">
+        <v>0.045</v>
+      </c>
+      <c r="Y8">
+        <v>0.094</v>
+      </c>
+      <c r="Z8">
+        <v>0.07</v>
+      </c>
+      <c r="AA8">
+        <v>0.103</v>
+      </c>
+      <c r="AB8">
+        <v>0.078</v>
+      </c>
+      <c r="AC8">
+        <v>0.106</v>
+      </c>
+      <c r="AD8">
+        <v>0.069</v>
+      </c>
+      <c r="AE8">
+        <v>0.073</v>
+      </c>
+      <c r="AF8">
+        <v>0.054</v>
+      </c>
+      <c r="AG8">
+        <v>0.058</v>
+      </c>
+      <c r="AH8">
+        <v>0.035</v>
+      </c>
+      <c r="AI8">
+        <v>0.04</v>
+      </c>
+      <c r="AJ8">
+        <v>0.024</v>
+      </c>
+      <c r="AK8">
+        <v>0.019</v>
+      </c>
+      <c r="AL8">
+        <v>0.014</v>
+      </c>
+      <c r="AM8">
+        <v>0.012</v>
+      </c>
+      <c r="AN8">
+        <v>0.023</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40">
+      <c r="A9">
+        <v>824120</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9">
+        <v>5.243</v>
+      </c>
+      <c r="F9">
+        <v>5.423</v>
+      </c>
+      <c r="G9">
+        <v>0.454</v>
+      </c>
+      <c r="H9">
+        <v>0.546</v>
+      </c>
+      <c r="I9">
+        <v>0.259</v>
+      </c>
+      <c r="J9">
+        <v>0.084</v>
+      </c>
+      <c r="K9">
+        <v>0.111</v>
+      </c>
+      <c r="L9">
+        <v>0.282</v>
+      </c>
+      <c r="M9">
+        <v>0.106</v>
+      </c>
+      <c r="N9">
+        <v>0.158</v>
+      </c>
+      <c r="O9">
+        <v>0.557</v>
+      </c>
+      <c r="P9">
+        <v>2.764</v>
+      </c>
+      <c r="Q9">
+        <v>3.238</v>
+      </c>
+      <c r="R9">
+        <v>0.38</v>
+      </c>
+      <c r="S9">
+        <v>0.489</v>
+      </c>
+      <c r="T9">
+        <v>0.0</v>
+      </c>
+      <c r="U9">
+        <v>0.006</v>
+      </c>
+      <c r="V9">
+        <v>0.007</v>
+      </c>
+      <c r="W9">
+        <v>0.028</v>
+      </c>
+      <c r="X9">
+        <v>0.026</v>
+      </c>
+      <c r="Y9">
+        <v>0.067</v>
+      </c>
+      <c r="Z9">
+        <v>0.052</v>
+      </c>
+      <c r="AA9">
+        <v>0.085</v>
+      </c>
+      <c r="AB9">
+        <v>0.078</v>
+      </c>
+      <c r="AC9">
+        <v>0.096</v>
+      </c>
+      <c r="AD9">
+        <v>0.075</v>
+      </c>
+      <c r="AE9">
+        <v>0.091</v>
+      </c>
+      <c r="AF9">
+        <v>0.063</v>
+      </c>
+      <c r="AG9">
+        <v>0.075</v>
+      </c>
+      <c r="AH9">
+        <v>0.049</v>
+      </c>
+      <c r="AI9">
+        <v>0.052</v>
+      </c>
+      <c r="AJ9">
+        <v>0.035</v>
+      </c>
+      <c r="AK9">
+        <v>0.035</v>
+      </c>
+      <c r="AL9">
+        <v>0.021</v>
+      </c>
+      <c r="AM9">
+        <v>0.017</v>
+      </c>
+      <c r="AN9">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40">
+      <c r="A10">
+        <v>824201</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10">
+        <v>5.165</v>
+      </c>
+      <c r="F10">
+        <v>4.036</v>
+      </c>
+      <c r="G10">
+        <v>0.586</v>
+      </c>
+      <c r="H10">
+        <v>0.414</v>
+      </c>
+      <c r="I10">
+        <v>0.36</v>
+      </c>
+      <c r="J10">
+        <v>0.103</v>
+      </c>
+      <c r="K10">
+        <v>0.123</v>
+      </c>
+      <c r="L10">
+        <v>0.174</v>
+      </c>
+      <c r="M10">
+        <v>0.086</v>
+      </c>
+      <c r="N10">
+        <v>0.155</v>
+      </c>
+      <c r="O10">
+        <v>0.487</v>
+      </c>
+      <c r="P10">
+        <v>2.782</v>
+      </c>
+      <c r="Q10">
+        <v>2.143</v>
+      </c>
+      <c r="R10">
+        <v>0.512</v>
+      </c>
+      <c r="S10">
+        <v>0.349</v>
+      </c>
+      <c r="T10">
+        <v>0.0</v>
+      </c>
+      <c r="U10">
+        <v>0.014</v>
+      </c>
+      <c r="V10">
+        <v>0.014</v>
+      </c>
+      <c r="W10">
+        <v>0.054</v>
+      </c>
+      <c r="X10">
+        <v>0.05</v>
+      </c>
+      <c r="Y10">
+        <v>0.083</v>
+      </c>
+      <c r="Z10">
+        <v>0.071</v>
+      </c>
+      <c r="AA10">
+        <v>0.097</v>
+      </c>
+      <c r="AB10">
+        <v>0.083</v>
+      </c>
+      <c r="AC10">
+        <v>0.106</v>
+      </c>
+      <c r="AD10">
+        <v>0.079</v>
+      </c>
+      <c r="AE10">
+        <v>0.084</v>
+      </c>
+      <c r="AF10">
+        <v>0.05</v>
+      </c>
+      <c r="AG10">
+        <v>0.057</v>
+      </c>
+      <c r="AH10">
+        <v>0.04</v>
+      </c>
+      <c r="AI10">
+        <v>0.031</v>
+      </c>
+      <c r="AJ10">
+        <v>0.021</v>
+      </c>
+      <c r="AK10">
+        <v>0.022</v>
+      </c>
+      <c r="AL10">
+        <v>0.017</v>
+      </c>
+      <c r="AM10">
+        <v>0.01</v>
+      </c>
+      <c r="AN10">
+        <v>0.017</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40">
+      <c r="A11">
+        <v>824283</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11">
+        <v>4.177</v>
+      </c>
+      <c r="F11">
+        <v>5.456</v>
+      </c>
+      <c r="G11">
+        <v>0.365</v>
+      </c>
+      <c r="H11">
+        <v>0.635</v>
+      </c>
+      <c r="I11">
+        <v>0.178</v>
+      </c>
+      <c r="J11">
+        <v>0.084</v>
+      </c>
+      <c r="K11">
+        <v>0.103</v>
+      </c>
+      <c r="L11">
+        <v>0.358</v>
+      </c>
+      <c r="M11">
+        <v>0.107</v>
+      </c>
+      <c r="N11">
+        <v>0.17</v>
+      </c>
+      <c r="O11">
+        <v>0.503</v>
+      </c>
+      <c r="P11">
+        <v>2.164</v>
+      </c>
+      <c r="Q11">
+        <v>3.172</v>
+      </c>
+      <c r="R11">
+        <v>0.309</v>
+      </c>
+      <c r="S11">
+        <v>0.54</v>
+      </c>
+      <c r="T11">
+        <v>0.0</v>
+      </c>
+      <c r="U11">
+        <v>0.013</v>
+      </c>
+      <c r="V11">
+        <v>0.016</v>
+      </c>
+      <c r="W11">
+        <v>0.048</v>
+      </c>
+      <c r="X11">
+        <v>0.041</v>
+      </c>
+      <c r="Y11">
+        <v>0.075</v>
+      </c>
+      <c r="Z11">
+        <v>0.067</v>
+      </c>
+      <c r="AA11">
+        <v>0.102</v>
+      </c>
+      <c r="AB11">
+        <v>0.075</v>
+      </c>
+      <c r="AC11">
+        <v>0.099</v>
+      </c>
+      <c r="AD11">
+        <v>0.069</v>
+      </c>
+      <c r="AE11">
+        <v>0.087</v>
+      </c>
+      <c r="AF11">
+        <v>0.064</v>
+      </c>
+      <c r="AG11">
+        <v>0.061</v>
+      </c>
+      <c r="AH11">
+        <v>0.039</v>
+      </c>
+      <c r="AI11">
+        <v>0.039</v>
+      </c>
+      <c r="AJ11">
+        <v>0.025</v>
+      </c>
+      <c r="AK11">
+        <v>0.024</v>
+      </c>
+      <c r="AL11">
+        <v>0.011</v>
+      </c>
+      <c r="AM11">
+        <v>0.013</v>
+      </c>
+      <c r="AN11">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40">
+      <c r="A12">
+        <v>824363</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12">
+        <v>6.334</v>
+      </c>
+      <c r="F12">
+        <v>6.435</v>
+      </c>
+      <c r="G12">
+        <v>0.474</v>
+      </c>
+      <c r="H12">
+        <v>0.526</v>
+      </c>
+      <c r="I12">
+        <v>0.299</v>
+      </c>
+      <c r="J12">
+        <v>0.078</v>
+      </c>
+      <c r="K12">
+        <v>0.096</v>
+      </c>
+      <c r="L12">
+        <v>0.3</v>
+      </c>
+      <c r="M12">
+        <v>0.091</v>
+      </c>
+      <c r="N12">
+        <v>0.135</v>
+      </c>
+      <c r="O12">
+        <v>0.589</v>
+      </c>
+      <c r="P12">
+        <v>3.45</v>
+      </c>
+      <c r="Q12">
+        <v>3.859</v>
+      </c>
+      <c r="R12">
+        <v>0.414</v>
+      </c>
+      <c r="S12">
+        <v>0.476</v>
+      </c>
+      <c r="T12">
+        <v>0.0</v>
+      </c>
+      <c r="U12">
+        <v>0.001</v>
+      </c>
+      <c r="V12">
+        <v>0.007</v>
+      </c>
+      <c r="W12">
+        <v>0.011</v>
+      </c>
+      <c r="X12">
+        <v>0.017</v>
+      </c>
+      <c r="Y12">
+        <v>0.028</v>
+      </c>
+      <c r="Z12">
+        <v>0.033</v>
+      </c>
+      <c r="AA12">
+        <v>0.063</v>
+      </c>
+      <c r="AB12">
+        <v>0.043</v>
+      </c>
+      <c r="AC12">
+        <v>0.085</v>
+      </c>
+      <c r="AD12">
+        <v>0.064</v>
+      </c>
+      <c r="AE12">
+        <v>0.095</v>
+      </c>
+      <c r="AF12">
+        <v>0.068</v>
+      </c>
+      <c r="AG12">
+        <v>0.086</v>
+      </c>
+      <c r="AH12">
+        <v>0.056</v>
+      </c>
+      <c r="AI12">
+        <v>0.07</v>
+      </c>
+      <c r="AJ12">
+        <v>0.048</v>
+      </c>
+      <c r="AK12">
+        <v>0.056</v>
+      </c>
+      <c r="AL12">
+        <v>0.029</v>
+      </c>
+      <c r="AM12">
+        <v>0.033</v>
+      </c>
+      <c r="AN12">
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13">
+        <v>824684</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13">
+        <v>5.968</v>
+      </c>
+      <c r="F13">
+        <v>7.472</v>
+      </c>
+      <c r="G13">
+        <v>0.356</v>
+      </c>
+      <c r="H13">
+        <v>0.644</v>
+      </c>
+      <c r="I13">
+        <v>0.205</v>
+      </c>
+      <c r="J13">
+        <v>0.065</v>
+      </c>
+      <c r="K13">
+        <v>0.087</v>
+      </c>
+      <c r="L13">
+        <v>0.41</v>
+      </c>
+      <c r="M13">
+        <v>0.091</v>
+      </c>
+      <c r="N13">
+        <v>0.142</v>
+      </c>
+      <c r="O13">
+        <v>0.616</v>
+      </c>
+      <c r="P13">
+        <v>3.28</v>
+      </c>
+      <c r="Q13">
+        <v>4.613</v>
+      </c>
+      <c r="R13">
+        <v>0.323</v>
+      </c>
+      <c r="S13">
+        <v>0.578</v>
+      </c>
+      <c r="T13">
+        <v>0.0</v>
+      </c>
+      <c r="U13">
+        <v>0.002</v>
+      </c>
+      <c r="V13">
+        <v>0.002</v>
+      </c>
+      <c r="W13">
+        <v>0.011</v>
+      </c>
+      <c r="X13">
+        <v>0.01</v>
+      </c>
+      <c r="Y13">
+        <v>0.027</v>
+      </c>
+      <c r="Z13">
+        <v>0.027</v>
+      </c>
+      <c r="AA13">
+        <v>0.052</v>
+      </c>
+      <c r="AB13">
+        <v>0.049</v>
+      </c>
+      <c r="AC13">
+        <v>0.077</v>
+      </c>
+      <c r="AD13">
+        <v>0.06</v>
+      </c>
+      <c r="AE13">
+        <v>0.076</v>
+      </c>
+      <c r="AF13">
+        <v>0.067</v>
+      </c>
+      <c r="AG13">
+        <v>0.083</v>
+      </c>
+      <c r="AH13">
+        <v>0.062</v>
+      </c>
+      <c r="AI13">
+        <v>0.067</v>
+      </c>
+      <c r="AJ13">
+        <v>0.053</v>
+      </c>
+      <c r="AK13">
+        <v>0.061</v>
+      </c>
+      <c r="AL13">
+        <v>0.037</v>
+      </c>
+      <c r="AM13">
+        <v>0.041</v>
+      </c>
+      <c r="AN13">
+        <v>0.135</v>
       </c>
     </row>
   </sheetData>
